--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N20_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>33.98856786208176</v>
       </c>
       <c r="E2" t="n">
-        <v>16.30842971091958</v>
+        <v>16.37329509785696</v>
       </c>
       <c r="F2" t="n">
-        <v>16.03140990149036</v>
+        <v>15.95437076577452</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>46.77741599485818</v>
       </c>
       <c r="E3" t="n">
-        <v>16.30842971091958</v>
+        <v>16.37329509785696</v>
       </c>
       <c r="F3" t="n">
-        <v>16.03140990149036</v>
+        <v>15.95437076577452</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>45.71542644434105</v>
       </c>
       <c r="E4" t="n">
-        <v>16.30842971091958</v>
+        <v>16.37329509785696</v>
       </c>
       <c r="F4" t="n">
-        <v>16.03140990149036</v>
+        <v>15.95437076577452</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>11.57211238882589</v>
       </c>
       <c r="E5" t="n">
-        <v>16.30842971091958</v>
+        <v>16.37329509785696</v>
       </c>
       <c r="F5" t="n">
-        <v>16.03140990149036</v>
+        <v>15.95437076577452</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         <v>4.956617410710861</v>
       </c>
       <c r="E6" t="n">
-        <v>16.30842971091958</v>
+        <v>16.37329509785696</v>
       </c>
       <c r="F6" t="n">
-        <v>16.03140990149036</v>
+        <v>15.95437076577452</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>37.56350373696351</v>
       </c>
       <c r="E7" t="n">
-        <v>16.30842971091958</v>
+        <v>16.37329509785696</v>
       </c>
       <c r="F7" t="n">
-        <v>16.03140990149036</v>
+        <v>15.95437076577452</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -678,10 +678,10 @@
         <v>48.27103375098905</v>
       </c>
       <c r="E8" t="n">
-        <v>16.30842971091958</v>
+        <v>16.37329509785696</v>
       </c>
       <c r="F8" t="n">
-        <v>16.03140990149036</v>
+        <v>15.95437076577452</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,23 +704,55 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
+        <v>12.99826823144052</v>
+      </c>
+      <c r="D9" t="n">
+        <v>14.52688553391882</v>
+      </c>
+      <c r="E9" t="n">
+        <v>16.37329509785696</v>
+      </c>
+      <c r="F9" t="n">
+        <v>15.95437076577452</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>T12594</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>W0065F0001T0006Z000C1N20.png</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
         <v>18.16076323439249</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>17.39988709819728</v>
       </c>
-      <c r="E9" t="n">
-        <v>16.30842971091958</v>
-      </c>
-      <c r="F9" t="n">
-        <v>16.03140990149036</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>T12594</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="E10" t="n">
+        <v>16.37329509785696</v>
+      </c>
+      <c r="F10" t="n">
+        <v>15.95437076577452</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>T12594</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.34667431981295</v>
+        <v>5.743834576969604</v>
       </c>
       <c r="D2" t="n">
-        <v>33.98856786208176</v>
+        <v>5.523142277588286</v>
       </c>
       <c r="E2" t="n">
-        <v>16.37329509785696</v>
+        <v>2.660660453401757</v>
       </c>
       <c r="F2" t="n">
-        <v>15.95437076577452</v>
+        <v>2.592585249438359</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.24343414725163</v>
+        <v>7.83955804892839</v>
       </c>
       <c r="D3" t="n">
-        <v>46.77741599485818</v>
+        <v>7.601330099164454</v>
       </c>
       <c r="E3" t="n">
-        <v>16.37329509785696</v>
+        <v>2.660660453401757</v>
       </c>
       <c r="F3" t="n">
-        <v>15.95437076577452</v>
+        <v>2.592585249438359</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.2285884109811</v>
+        <v>7.34964561678443</v>
       </c>
       <c r="D4" t="n">
-        <v>45.71542644434105</v>
+        <v>7.428756797205421</v>
       </c>
       <c r="E4" t="n">
-        <v>16.37329509785696</v>
+        <v>2.660660453401757</v>
       </c>
       <c r="F4" t="n">
-        <v>15.95437076577452</v>
+        <v>2.592585249438359</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.73677511579108</v>
+        <v>1.74472595631605</v>
       </c>
       <c r="D5" t="n">
-        <v>11.57211238882589</v>
+        <v>1.880468263184207</v>
       </c>
       <c r="E5" t="n">
-        <v>16.37329509785696</v>
+        <v>2.660660453401757</v>
       </c>
       <c r="F5" t="n">
-        <v>15.95437076577452</v>
+        <v>2.592585249438359</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>4.399551130393212</v>
+        <v>0.7149270586888969</v>
       </c>
       <c r="D6" t="n">
-        <v>4.956617410710861</v>
+        <v>0.805450329240515</v>
       </c>
       <c r="E6" t="n">
-        <v>16.37329509785696</v>
+        <v>2.660660453401757</v>
       </c>
       <c r="F6" t="n">
-        <v>15.95437076577452</v>
+        <v>2.592585249438359</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.15209620750333</v>
+        <v>6.037215633719292</v>
       </c>
       <c r="D7" t="n">
-        <v>37.56350373696351</v>
+        <v>6.104069357256571</v>
       </c>
       <c r="E7" t="n">
-        <v>16.37329509785696</v>
+        <v>2.660660453401757</v>
       </c>
       <c r="F7" t="n">
-        <v>15.95437076577452</v>
+        <v>2.592585249438359</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>47.97738090071087</v>
+        <v>7.796324396365517</v>
       </c>
       <c r="D8" t="n">
-        <v>48.27103375098905</v>
+        <v>7.84404298453572</v>
       </c>
       <c r="E8" t="n">
-        <v>16.37329509785696</v>
+        <v>2.660660453401757</v>
       </c>
       <c r="F8" t="n">
-        <v>15.95437076577452</v>
+        <v>2.592585249438359</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>12.99826823144052</v>
+        <v>2.112218587609084</v>
       </c>
       <c r="D9" t="n">
-        <v>14.52688553391882</v>
+        <v>2.360618899261808</v>
       </c>
       <c r="E9" t="n">
-        <v>16.37329509785696</v>
+        <v>2.660660453401757</v>
       </c>
       <c r="F9" t="n">
-        <v>15.95437076577452</v>
+        <v>2.592585249438359</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.16076323439249</v>
+        <v>2.951124025588781</v>
       </c>
       <c r="D10" t="n">
-        <v>17.39988709819728</v>
+        <v>2.827481653457058</v>
       </c>
       <c r="E10" t="n">
-        <v>16.37329509785696</v>
+        <v>2.660660453401757</v>
       </c>
       <c r="F10" t="n">
-        <v>15.95437076577452</v>
+        <v>2.592585249438359</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
